--- a/data/trans_dic/IP22_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,49; 38,39</t>
+          <t>24,57; 38,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,08; 40,92</t>
+          <t>27,89; 40,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,47; 28,05</t>
+          <t>16,59; 27,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 36,28</t>
+          <t>19,27; 36,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,61; 34,81</t>
+          <t>21,66; 34,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,96; 34,37</t>
+          <t>21,85; 33,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,17; 26,35</t>
+          <t>13,77; 25,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,84; 31,34</t>
+          <t>13,81; 31,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,48; 34,3</t>
+          <t>24,38; 34,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,96; 35,89</t>
+          <t>27,15; 35,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 25,26</t>
+          <t>16,29; 24,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,31; 30,15</t>
+          <t>17,92; 30,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 24,67</t>
+          <t>16,23; 24,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,92; 37,54</t>
+          <t>26,71; 36,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 26,06</t>
+          <t>17,24; 26,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 19,76</t>
+          <t>9,91; 20,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,65; 31,83</t>
+          <t>23,07; 31,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,06; 40,96</t>
+          <t>31,0; 41,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,87; 20,65</t>
+          <t>13,17; 20,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 23,2</t>
+          <t>12,77; 22,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,51; 26,74</t>
+          <t>20,97; 27,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,6; 37,64</t>
+          <t>30,27; 37,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,89; 21,71</t>
+          <t>15,83; 21,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 19,58</t>
+          <t>12,66; 19,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 22,7</t>
+          <t>12,19; 22,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 19,27</t>
+          <t>10,26; 19,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,48; 20,92</t>
+          <t>12,2; 20,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,81; 19,94</t>
+          <t>10,23; 19,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 19,57</t>
+          <t>10,62; 20,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,95; 23,27</t>
+          <t>12,68; 23,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,17; 21,28</t>
+          <t>12,09; 21,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,95; 21,71</t>
+          <t>11,36; 21,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,28; 19,42</t>
+          <t>12,45; 19,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,72; 19,37</t>
+          <t>12,45; 19,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,74</t>
+          <t>13,35; 19,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,65; 19,16</t>
+          <t>12,14; 19,05</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,91; 17,94</t>
+          <t>10,08; 18,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 15,53</t>
+          <t>7,32; 15,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 16,36</t>
+          <t>7,45; 15,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 20,32</t>
+          <t>9,94; 21,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,77; 21,24</t>
+          <t>12,53; 20,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,69; 29,04</t>
+          <t>19,28; 29,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,55; 21,15</t>
+          <t>10,99; 20,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 16,58</t>
+          <t>9,23; 17,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,19; 18,08</t>
+          <t>12,04; 17,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,53; 21,27</t>
+          <t>14,59; 21,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 16,62</t>
+          <t>10,7; 16,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 16,96</t>
+          <t>10,43; 17,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,86; 21,77</t>
+          <t>16,86; 21,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 26,33</t>
+          <t>20,83; 26,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 20,33</t>
+          <t>15,42; 19,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 18,64</t>
+          <t>12,64; 18,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 24,25</t>
+          <t>19,37; 24,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,97; 30,5</t>
+          <t>24,91; 30,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,56; 19,17</t>
+          <t>14,55; 19,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,08; 18,11</t>
+          <t>13,07; 17,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,85; 22,22</t>
+          <t>18,82; 22,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,74; 27,66</t>
+          <t>23,84; 27,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,87</t>
+          <t>15,48; 18,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,75; 17,63</t>
+          <t>13,63; 17,65</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25998; 40761</t>
+          <t>26090; 40963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41211; 60060</t>
+          <t>40934; 59849</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21679; 36925</t>
+          <t>21845; 36462</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10646; 20866</t>
+          <t>11085; 20783</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26226; 42249</t>
+          <t>26296; 42160</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31717; 49637</t>
+          <t>31554; 48971</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17598; 32718</t>
+          <t>17103; 31896</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8506; 19256</t>
+          <t>8484; 19442</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55704; 78043</t>
+          <t>55470; 78300</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78494; 104496</t>
+          <t>79062; 103988</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43328; 64617</t>
+          <t>41675; 63469</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21775; 35862</t>
+          <t>21311; 36105</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41617; 62474</t>
+          <t>41086; 62047</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63427; 88440</t>
+          <t>62938; 86707</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36228; 54867</t>
+          <t>36289; 54775</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16520; 31480</t>
+          <t>15788; 32046</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57474; 80781</t>
+          <t>58545; 80581</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83312; 109886</t>
+          <t>83149; 111148</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33200; 53295</t>
+          <t>33997; 52168</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22799; 42360</t>
+          <t>23305; 41606</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>103980; 135564</t>
+          <t>106307; 137160</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>154162; 189674</t>
+          <t>152512; 188413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74470; 101727</t>
+          <t>74172; 101160</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41743; 66938</t>
+          <t>43275; 66350</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15115; 28959</t>
+          <t>15554; 29050</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15590; 30259</t>
+          <t>16112; 30551</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23581; 39509</t>
+          <t>23052; 39498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18633; 34366</t>
+          <t>17635; 34170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14438; 27699</t>
+          <t>15025; 28334</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20543; 36895</t>
+          <t>20109; 36779</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22954; 40122</t>
+          <t>22796; 39939</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25401; 46134</t>
+          <t>24148; 46178</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33029; 52253</t>
+          <t>33504; 52936</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40142; 61125</t>
+          <t>39295; 62263</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50910; 74504</t>
+          <t>50393; 73726</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48677; 73726</t>
+          <t>46732; 73312</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19243; 34812</t>
+          <t>19564; 35898</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13186; 26603</t>
+          <t>12549; 26130</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14036; 28356</t>
+          <t>12914; 26079</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26638; 55977</t>
+          <t>27373; 58827</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26313; 43757</t>
+          <t>25810; 43123</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33464; 52014</t>
+          <t>34538; 53068</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20014; 36638</t>
+          <t>19039; 35418</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27085; 50664</t>
+          <t>28203; 51951</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48769; 72331</t>
+          <t>48174; 71644</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50906; 74524</t>
+          <t>51132; 74286</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36944; 57590</t>
+          <t>37081; 58860</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59699; 98522</t>
+          <t>60603; 98741</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>114820; 148284</t>
+          <t>114811; 148370</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>149607; 187162</t>
+          <t>148063; 187006</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109625; 143203</t>
+          <t>108595; 140126</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84455; 123880</t>
+          <t>84008; 124638</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>139843; 175288</t>
+          <t>140014; 175099</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>187350; 228833</t>
+          <t>186934; 227835</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>108303; 142659</t>
+          <t>108277; 141691</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99644; 138030</t>
+          <t>99617; 135313</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>264539; 311881</t>
+          <t>264161; 315664</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>346823; 404113</t>
+          <t>348333; 403716</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227897; 273282</t>
+          <t>224244; 271598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>196171; 251523</t>
+          <t>194422; 251730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP22_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27,5%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,34%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20,85%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>31,22%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>34,76%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>21,77%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26,23%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,57; 38,58</t>
+          <t>21,5; 33,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,89; 40,78</t>
+          <t>22,19; 34,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 27,7</t>
+          <t>13,78; 26,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,27; 36,14</t>
+          <t>13,65; 29,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,66; 34,73</t>
+          <t>24,66; 39,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,85; 33,91</t>
+          <t>29,17; 41,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,77; 25,69</t>
+          <t>16,77; 28,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 31,64</t>
+          <t>18,56; 35,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,38; 34,41</t>
+          <t>24,98; 34,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,15; 35,71</t>
+          <t>26,55; 36,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,29; 24,81</t>
+          <t>16,54; 24,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 30,35</t>
+          <t>17,96; 30,27</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27,17%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,36%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16,31%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>20,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>31,96%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>21,5%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>27,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,23; 24,5</t>
+          <t>23,3; 31,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,71; 36,8</t>
+          <t>31,09; 40,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 26,02</t>
+          <t>12,87; 20,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,91; 20,12</t>
+          <t>12,01; 21,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,07; 31,76</t>
+          <t>16,28; 24,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,0; 41,43</t>
+          <t>26,71; 36,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 20,22</t>
+          <t>17,37; 26,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 22,79</t>
+          <t>9,78; 19,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,97; 27,06</t>
+          <t>20,74; 26,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,27; 37,39</t>
+          <t>30,55; 37,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,83; 21,59</t>
+          <t>15,98; 21,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 19,41</t>
+          <t>12,06; 18,72</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16,55%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14,41%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16,2%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,85%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,19; 22,78</t>
+          <t>10,54; 20,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 19,45</t>
+          <t>12,57; 22,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,2; 20,91</t>
+          <t>11,91; 21,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 19,83</t>
+          <t>11,56; 21,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 20,02</t>
+          <t>11,79; 22,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 23,19</t>
+          <t>10,12; 19,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,09; 21,18</t>
+          <t>12,17; 20,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 21,73</t>
+          <t>10,42; 19,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 19,67</t>
+          <t>12,16; 19,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 19,73</t>
+          <t>12,65; 19,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,35; 19,53</t>
+          <t>13,18; 19,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,14; 19,05</t>
+          <t>12,31; 19,28</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,45%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,47%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11,02%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,28%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 18,5</t>
+          <t>12,63; 21,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,25</t>
+          <t>18,85; 29,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 15,05</t>
+          <t>11,6; 20,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 21,36</t>
+          <t>8,72; 16,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 20,93</t>
+          <t>9,8; 17,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,28; 29,63</t>
+          <t>7,28; 15,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 20,45</t>
+          <t>7,92; 15,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 17,01</t>
+          <t>10,98; 18,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,04; 17,9</t>
+          <t>12,27; 18,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,59; 21,2</t>
+          <t>14,31; 20,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 16,99</t>
+          <t>10,93; 16,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 17,0</t>
+          <t>11,01; 16,49</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,73%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>19,33%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>23,61%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>17,62%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,86; 21,79</t>
+          <t>19,2; 24,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,83; 26,31</t>
+          <t>25,01; 30,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,42; 19,89</t>
+          <t>14,51; 19,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,64; 18,75</t>
+          <t>12,93; 17,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,37; 24,23</t>
+          <t>17,06; 21,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,91; 30,36</t>
+          <t>21,26; 26,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 19,04</t>
+          <t>15,45; 19,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 17,76</t>
+          <t>12,96; 17,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 22,49</t>
+          <t>18,8; 22,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,84; 27,63</t>
+          <t>23,92; 27,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,48; 18,75</t>
+          <t>15,63; 18,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 17,65</t>
+          <t>13,28; 17,05</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33377</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40102</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24016</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10538</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>33143</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>51020</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>28663</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15085</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>33377</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40102</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24016</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>23964</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26090; 40963</t>
+          <t>26102; 41141</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40934; 59849</t>
+          <t>32047; 49403</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21845; 36462</t>
+          <t>17108; 32454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11085; 20783</t>
+          <t>6896; 14705</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26296; 42160</t>
+          <t>26185; 41609</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31554; 48971</t>
+          <t>42814; 60806</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17103; 31896</t>
+          <t>22076; 37120</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8484; 19442</t>
+          <t>9665; 18667</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55470; 78300</t>
+          <t>56852; 78758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79062; 103988</t>
+          <t>77313; 105656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41675; 63469</t>
+          <t>42317; 63287</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21311; 36105</t>
+          <t>18436; 31062</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>68943</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96303</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>42209</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25694</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>51262</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>75294</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>45267</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22728</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>68943</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96303</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42209</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54005</t>
+          <t>45694</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41086; 62047</t>
+          <t>59115; 80740</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62938; 86707</t>
+          <t>83388; 109902</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36289; 54775</t>
+          <t>33212; 52116</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15788; 32046</t>
+          <t>18925; 34632</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58545; 80581</t>
+          <t>41214; 61300</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83149; 111148</t>
+          <t>62921; 86563</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33997; 52168</t>
+          <t>36576; 55254</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23305; 41606</t>
+          <t>14228; 27669</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>106307; 137160</t>
+          <t>105164; 135389</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>152512; 188413</t>
+          <t>153915; 189703</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74172; 101160</t>
+          <t>74894; 100368</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43275; 66350</t>
+          <t>36554; 56714</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20810</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27582</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30963</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32225</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>21108</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>22629</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>30604</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25591</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20810</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27582</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30963</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59988</t>
+          <t>57989</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15554; 29050</t>
+          <t>14911; 28817</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16112; 30551</t>
+          <t>19939; 36413</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23052; 39498</t>
+          <t>22459; 40211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17635; 34170</t>
+          <t>23126; 42399</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15025; 28334</t>
+          <t>15041; 28281</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20109; 36779</t>
+          <t>15899; 30934</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22796; 39939</t>
+          <t>22985; 39194</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24148; 46178</t>
+          <t>18129; 33741</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33504; 52936</t>
+          <t>32711; 51522</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39295; 62263</t>
+          <t>39918; 61036</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50393; 73726</t>
+          <t>49762; 73479</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46732; 73312</t>
+          <t>46070; 72129</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33899</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42830</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27340</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37165</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>26148</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>18874</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>19550</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>39831</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>33899</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>42830</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27340</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77752</t>
+          <t>73762</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19564; 35898</t>
+          <t>26015; 43766</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12549; 26130</t>
+          <t>33767; 52126</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12914; 26079</t>
+          <t>20087; 35605</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27373; 58827</t>
+          <t>25504; 48551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25810; 43123</t>
+          <t>19022; 34145</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34538; 53068</t>
+          <t>12466; 26056</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19039; 35418</t>
+          <t>13717; 26805</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28203; 51951</t>
+          <t>28157; 47950</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48174; 71644</t>
+          <t>49081; 72200</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51132; 74286</t>
+          <t>50131; 72672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37081; 58860</t>
+          <t>37875; 58718</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>60603; 98741</t>
+          <t>60483; 90568</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>243</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>149</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>157029</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>206817</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124527</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>105622</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>131661</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>167818</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>124084</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>103235</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>157029</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>206817</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>124527</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>116838</t>
+          <t>95788</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>220073</t>
+          <t>201409</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>114811; 148370</t>
+          <t>138749; 177154</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148063; 187006</t>
+          <t>187656; 230418</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108595; 140126</t>
+          <t>107955; 142338</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84008; 124638</t>
+          <t>90588; 125160</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>140014; 175099</t>
+          <t>116201; 149172</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>186934; 227835</t>
+          <t>151095; 186466</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>108277; 141691</t>
+          <t>108859; 140183</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99617; 135313</t>
+          <t>81393; 111298</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>264161; 315664</t>
+          <t>263954; 313393</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348333; 403716</t>
+          <t>349557; 404110</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>224244; 271598</t>
+          <t>226452; 272633</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>194422; 251730</t>
+          <t>176479; 226552</t>
         </is>
       </c>
     </row>
